--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.01126605756680635</v>
+        <v>0.112911224263892</v>
       </c>
       <c r="H2">
-        <v>-0.1683726042453802</v>
+        <v>-0.005308833296435687</v>
       </c>
       <c r="I2">
-        <v>-0.0728858968193996</v>
+        <v>-0.1279656226677155</v>
       </c>
       <c r="J2">
-        <v>-0.0728858968193996</v>
+        <v>-0.1279656226677155</v>
       </c>
       <c r="K2">
-        <v>-421.3</v>
+        <v>-611.7</v>
       </c>
       <c r="L2">
-        <v>-0.2894140276155801</v>
+        <v>-0.4514058003099403</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>668.6</v>
+        <v>860</v>
       </c>
       <c r="V2">
-        <v>0.3133670791151106</v>
+        <v>0.6454033771106942</v>
       </c>
       <c r="W2">
-        <v>-0.444456166262264</v>
+        <v>-0.6574591573516768</v>
       </c>
       <c r="X2">
-        <v>0.1003422909111469</v>
+        <v>0.1487547797355883</v>
       </c>
       <c r="Y2">
-        <v>-0.5447984571734109</v>
+        <v>-0.8062139370872651</v>
       </c>
       <c r="Z2">
-        <v>0.6982779296781312</v>
+        <v>0.6694922998554692</v>
       </c>
       <c r="AA2">
-        <v>-0.05089461313378424</v>
+        <v>0.3145460274717174</v>
       </c>
       <c r="AB2">
-        <v>0.06820247240600429</v>
+        <v>0.1252211927905641</v>
       </c>
       <c r="AC2">
-        <v>-0.1190970855397885</v>
+        <v>0.1893248346811533</v>
       </c>
       <c r="AD2">
-        <v>1762</v>
+        <v>1790.9</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.2710763851062756</v>
       </c>
       <c r="AF2">
-        <v>1762</v>
+        <v>1791.171076385106</v>
       </c>
       <c r="AG2">
-        <v>1093.4</v>
+        <v>931.1710763851063</v>
       </c>
       <c r="AH2">
-        <v>0.4523051648013143</v>
+        <v>0.5734185938866373</v>
       </c>
       <c r="AI2">
-        <v>0.6544347050958252</v>
+        <v>0.6718896094607529</v>
       </c>
       <c r="AJ2">
-        <v>0.33882863340564</v>
+        <v>0.4113544083763745</v>
       </c>
       <c r="AK2">
-        <v>0.5402707777448365</v>
+        <v>0.5156354119415177</v>
       </c>
       <c r="AL2">
-        <v>195.6</v>
+        <v>202.2</v>
       </c>
       <c r="AM2">
-        <v>192.49</v>
+        <v>199.64</v>
       </c>
       <c r="AN2">
-        <v>178.7018255578093</v>
+        <v>-110.1956682254492</v>
       </c>
       <c r="AO2">
-        <v>-0.5424335378323109</v>
+        <v>-0.8585558852621168</v>
       </c>
       <c r="AP2">
-        <v>110.8924949290061</v>
+        <v>-57.29578368109195</v>
       </c>
       <c r="AQ2">
-        <v>-0.5511974648033664</v>
+        <v>-0.8695652173913043</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda Global Holdings plc (LSE:AML)</t>
+          <t>Aurrigo International plc (AIM:AURR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,23 +712,8 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0.01126605756680635</v>
-      </c>
-      <c r="H3">
-        <v>-0.1683726042453802</v>
-      </c>
-      <c r="I3">
-        <v>-0.0728858968193996</v>
-      </c>
-      <c r="J3">
-        <v>-0.0728858968193996</v>
-      </c>
       <c r="K3">
-        <v>-421.3</v>
-      </c>
-      <c r="L3">
-        <v>-0.2894140276155801</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -736,89 +721,196 @@
       <c r="N3">
         <v>-0</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>668.6</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.3133670791151106</v>
-      </c>
-      <c r="W3">
-        <v>-0.444456166262264</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1003422909111469</v>
-      </c>
-      <c r="Y3">
-        <v>-0.5447984571734109</v>
+        <v>0.1115373927214055</v>
       </c>
       <c r="Z3">
-        <v>0.6982779296781312</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.05089461313378424</v>
+        <v>0.7148712821397981</v>
       </c>
       <c r="AB3">
-        <v>0.06820247240600429</v>
+        <v>0.1110600233807317</v>
       </c>
       <c r="AC3">
-        <v>-0.1190970855397885</v>
+        <v>0.6038112587590665</v>
       </c>
       <c r="AD3">
-        <v>1762</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.2710763851062756</v>
       </c>
       <c r="AF3">
-        <v>1762</v>
+        <v>0.2710763851062756</v>
       </c>
       <c r="AG3">
-        <v>1093.4</v>
+        <v>0.2710763851062756</v>
       </c>
       <c r="AH3">
-        <v>0.4523051648013143</v>
+        <v>0.007707366761770958</v>
       </c>
       <c r="AI3">
-        <v>0.6544347050958252</v>
+        <v>1</v>
       </c>
       <c r="AJ3">
-        <v>0.33882863340564</v>
+        <v>0.007707366761770958</v>
       </c>
       <c r="AK3">
-        <v>0.5402707777448365</v>
+        <v>1</v>
       </c>
       <c r="AL3">
-        <v>195.6</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>192.49</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>178.7018255578093</v>
-      </c>
-      <c r="AO3">
-        <v>-0.5424335378323109</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>110.8924949290061</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.5511974648033664</v>
+        <v>1.09304993994466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aston Martin Lagonda Global Holdings plc (LSE:AML)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.113024869013357</v>
+      </c>
+      <c r="H4">
+        <v>-0.005195188546970704</v>
+      </c>
+      <c r="I4">
+        <v>-0.1281086266696185</v>
+      </c>
+      <c r="J4">
+        <v>-0.1281086266696185</v>
+      </c>
+      <c r="K4">
+        <v>-611.7</v>
+      </c>
+      <c r="L4">
+        <v>-0.4514058003099403</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>860</v>
+      </c>
+      <c r="V4">
+        <v>0.6627620221948213</v>
+      </c>
+      <c r="W4">
+        <v>-0.6574591573516768</v>
+      </c>
+      <c r="X4">
+        <v>0.185972166749771</v>
+      </c>
+      <c r="Y4">
+        <v>-0.8434313241014478</v>
+      </c>
+      <c r="Z4">
+        <v>0.6695819745034093</v>
+      </c>
+      <c r="AA4">
+        <v>-0.08577922719636327</v>
+      </c>
+      <c r="AB4">
+        <v>0.1393823622003966</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2251615893967599</v>
+      </c>
+      <c r="AD4">
+        <v>1790.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1790.9</v>
+      </c>
+      <c r="AG4">
+        <v>930.9000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.5798607738384329</v>
+      </c>
+      <c r="AI4">
+        <v>0.6718562424969987</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4177249270809962</v>
+      </c>
+      <c r="AK4">
+        <v>0.5155626938413824</v>
+      </c>
+      <c r="AL4">
+        <v>202.2</v>
+      </c>
+      <c r="AM4">
+        <v>199.64</v>
+      </c>
+      <c r="AN4">
+        <v>-108.5393939393939</v>
+      </c>
+      <c r="AO4">
+        <v>-0.8585558852621168</v>
+      </c>
+      <c r="AP4">
+        <v>-56.41818181818182</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.8695652173913043</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
@@ -587,23 +587,26 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.107</v>
+      </c>
       <c r="G2">
-        <v>0.112911224263892</v>
+        <v>0.127890567101239</v>
       </c>
       <c r="H2">
-        <v>-0.005308833296435687</v>
+        <v>-0.02349613268895546</v>
       </c>
       <c r="I2">
-        <v>-0.1279656226677155</v>
+        <v>-0.07603624103629322</v>
       </c>
       <c r="J2">
-        <v>-0.1279656226677155</v>
+        <v>-0.07603624103629322</v>
       </c>
       <c r="K2">
-        <v>-611.7</v>
+        <v>-335.11</v>
       </c>
       <c r="L2">
-        <v>-0.4514058003099403</v>
+        <v>-0.1748953581829379</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>860</v>
+        <v>667.15</v>
       </c>
       <c r="V2">
-        <v>0.6454033771106942</v>
-      </c>
-      <c r="W2">
-        <v>-0.6574591573516768</v>
+        <v>0.2757159978509732</v>
       </c>
       <c r="X2">
-        <v>0.1487547797355883</v>
-      </c>
-      <c r="Y2">
-        <v>-0.8062139370872651</v>
+        <v>0.1084250925123711</v>
       </c>
       <c r="Z2">
-        <v>0.6694922998554692</v>
-      </c>
-      <c r="AA2">
-        <v>0.3145460274717174</v>
+        <v>1.061176340274701</v>
       </c>
       <c r="AB2">
-        <v>0.1252211927905641</v>
-      </c>
-      <c r="AC2">
-        <v>0.1893248346811533</v>
+        <v>0.1008690956902438</v>
       </c>
       <c r="AD2">
-        <v>1790.9</v>
+        <v>1553.913</v>
       </c>
       <c r="AE2">
-        <v>0.2710763851062756</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1791.171076385106</v>
+        <v>1553.913</v>
       </c>
       <c r="AG2">
-        <v>931.1710763851063</v>
+        <v>886.763</v>
       </c>
       <c r="AH2">
-        <v>0.5734185938866373</v>
+        <v>0.3910579616082391</v>
       </c>
       <c r="AI2">
-        <v>0.6718896094607529</v>
+        <v>0.5981758080926093</v>
       </c>
       <c r="AJ2">
-        <v>0.4113544083763745</v>
+        <v>0.268190812962371</v>
       </c>
       <c r="AK2">
-        <v>0.5156354119415177</v>
+        <v>0.4593191868032941</v>
       </c>
       <c r="AL2">
-        <v>202.2</v>
+        <v>176.747</v>
       </c>
       <c r="AM2">
-        <v>199.64</v>
+        <v>173.022</v>
       </c>
       <c r="AN2">
-        <v>-110.1956682254492</v>
+        <v>56.81583180987203</v>
       </c>
       <c r="AO2">
-        <v>-0.8585558852621168</v>
+        <v>-0.8242855607167308</v>
       </c>
       <c r="AP2">
-        <v>-57.29578368109195</v>
+        <v>32.42277879341864</v>
       </c>
       <c r="AQ2">
-        <v>-0.8695652173913043</v>
+        <v>-0.8420316491544428</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aurrigo International plc (AIM:AURR)</t>
+          <t>Aston Martin Lagonda Global Holdings plc (LSE:AML)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,8 +703,26 @@
           <t>Auto &amp; Truck</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.107</v>
+      </c>
+      <c r="G3">
+        <v>0.1291201593040927</v>
+      </c>
+      <c r="H3">
+        <v>-0.02269035266991563</v>
+      </c>
+      <c r="I3">
+        <v>-0.07430697479431955</v>
+      </c>
+      <c r="J3">
+        <v>-0.07430697479431955</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>-330.2</v>
+      </c>
+      <c r="L3">
+        <v>-0.1730335901063774</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -721,71 +730,89 @@
       <c r="N3">
         <v>-0</v>
       </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>663.6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2803667244074528</v>
+      </c>
+      <c r="W3">
+        <v>-0.3775008574368355</v>
       </c>
       <c r="X3">
-        <v>0.1115373927214055</v>
+        <v>0.1217896710187427</v>
+      </c>
+      <c r="Y3">
+        <v>-0.4992905284555782</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.056878599911387</v>
       </c>
       <c r="AA3">
-        <v>0.7148712821397981</v>
+        <v>-0.07853345148427114</v>
       </c>
       <c r="AB3">
-        <v>0.1110600233807317</v>
+        <v>0.1074361893338245</v>
       </c>
       <c r="AC3">
-        <v>0.6038112587590665</v>
+        <v>-0.1859696408180956</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1553.1</v>
       </c>
       <c r="AE3">
-        <v>0.2710763851062756</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.2710763851062756</v>
+        <v>1553.1</v>
       </c>
       <c r="AG3">
-        <v>0.2710763851062756</v>
+        <v>889.4999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.007707366761770958</v>
+        <v>0.3961989795918367</v>
       </c>
       <c r="AI3">
-        <v>1</v>
+        <v>0.6000463624773016</v>
       </c>
       <c r="AJ3">
-        <v>0.007707366761770958</v>
+        <v>0.2731544036359169</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>0.4621499454460435</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>176.7</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>173.04</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>50.09999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>-0.8024900962082627</v>
       </c>
       <c r="AP3">
-        <v>1.09304993994466</v>
+        <v>28.69354838709677</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.8194637078132225</v>
       </c>
     </row>
     <row r="4">
@@ -796,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda Global Holdings plc (LSE:AML)</t>
+          <t>Aurrigo International plc (AIM:AURR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -805,22 +832,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.113024869013357</v>
+        <v>-0.1744845360824742</v>
       </c>
       <c r="H4">
-        <v>-0.005195188546970704</v>
+        <v>-0.2216494845360825</v>
       </c>
       <c r="I4">
-        <v>-0.1281086266696185</v>
+        <v>-0.5012886597938144</v>
       </c>
       <c r="J4">
-        <v>-0.1281086266696185</v>
+        <v>-0.5012886597938144</v>
       </c>
       <c r="K4">
-        <v>-611.7</v>
+        <v>-4.91</v>
       </c>
       <c r="L4">
-        <v>-0.4514058003099403</v>
+        <v>-0.6327319587628867</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -844,73 +871,58 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>860</v>
+        <v>3.55</v>
       </c>
       <c r="V4">
-        <v>0.6627620221948213</v>
-      </c>
-      <c r="W4">
-        <v>-0.6574591573516768</v>
+        <v>0.06723484848484848</v>
       </c>
       <c r="X4">
-        <v>0.185972166749771</v>
-      </c>
-      <c r="Y4">
-        <v>-0.8434313241014478</v>
-      </c>
-      <c r="Z4">
-        <v>0.6695819745034093</v>
-      </c>
-      <c r="AA4">
-        <v>-0.08577922719636327</v>
+        <v>0.09506051400599939</v>
       </c>
       <c r="AB4">
-        <v>0.1393823622003966</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2251615893967599</v>
+        <v>0.09430200204666304</v>
       </c>
       <c r="AD4">
-        <v>1790.9</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1790.9</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AG4">
-        <v>930.9000000000001</v>
+        <v>-2.737</v>
       </c>
       <c r="AH4">
-        <v>0.5798607738384329</v>
+        <v>0.0151642325555369</v>
       </c>
       <c r="AI4">
-        <v>0.6718562424969987</v>
+        <v>0.08600444303395746</v>
       </c>
       <c r="AJ4">
-        <v>0.4177249270809962</v>
+        <v>-0.05467111439586122</v>
       </c>
       <c r="AK4">
-        <v>0.5155626938413824</v>
+        <v>-0.4636625444689141</v>
       </c>
       <c r="AL4">
-        <v>202.2</v>
+        <v>0.047</v>
       </c>
       <c r="AM4">
-        <v>199.64</v>
+        <v>-0.018</v>
       </c>
       <c r="AN4">
-        <v>-108.5393939393939</v>
+        <v>-0.2227397260273973</v>
       </c>
       <c r="AO4">
-        <v>-0.8585558852621168</v>
+        <v>-82.76595744680851</v>
       </c>
       <c r="AP4">
-        <v>-56.41818181818182</v>
+        <v>0.7498630136986302</v>
       </c>
       <c r="AQ4">
-        <v>-0.8695652173913043</v>
+        <v>216.1111111111111</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.107</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G2">
-        <v>0.127890567101239</v>
+        <v>0.2033078043508904</v>
       </c>
       <c r="H2">
-        <v>-0.02349613268895546</v>
+        <v>0.01155852088521355</v>
       </c>
       <c r="I2">
-        <v>-0.07603624103629322</v>
+        <v>-0.04402574824977681</v>
       </c>
       <c r="J2">
-        <v>-0.07603624103629322</v>
+        <v>-0.04402574824977681</v>
       </c>
       <c r="K2">
-        <v>-335.11</v>
+        <v>-251.7</v>
       </c>
       <c r="L2">
-        <v>-0.1748953581829379</v>
+        <v>-0.1182634027157825</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,61 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>667.15</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.2757159978509732</v>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>-0.2431414219474498</v>
       </c>
       <c r="X2">
-        <v>0.1084250925123711</v>
+        <v>0.1553075502293048</v>
+      </c>
+      <c r="Y2">
+        <v>-0.3984489721767546</v>
       </c>
       <c r="Z2">
-        <v>1.061176340274701</v>
+        <v>1.105782719384839</v>
+      </c>
+      <c r="AA2">
+        <v>-0.04868291162259053</v>
       </c>
       <c r="AB2">
-        <v>0.1008690956902438</v>
+        <v>0.105729775026532</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1544126866491225</v>
       </c>
       <c r="AD2">
-        <v>1553.913</v>
+        <v>1831.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1553.913</v>
+        <v>1831.5</v>
       </c>
       <c r="AG2">
-        <v>886.763</v>
+        <v>1831.5</v>
       </c>
       <c r="AH2">
-        <v>0.3910579616082391</v>
+        <v>0.5947780339687591</v>
       </c>
       <c r="AI2">
-        <v>0.5981758080926093</v>
+        <v>0.6422710057511573</v>
       </c>
       <c r="AJ2">
-        <v>0.268190812962371</v>
+        <v>0.5947780339687591</v>
       </c>
       <c r="AK2">
-        <v>0.4593191868032941</v>
+        <v>0.6422710057511573</v>
       </c>
       <c r="AL2">
-        <v>176.747</v>
+        <v>206</v>
       </c>
       <c r="AM2">
-        <v>173.022</v>
-      </c>
-      <c r="AN2">
-        <v>56.81583180987203</v>
+        <v>187.9</v>
       </c>
       <c r="AO2">
-        <v>-0.8242855607167308</v>
-      </c>
-      <c r="AP2">
-        <v>32.42277879341864</v>
+        <v>-0.4548543689320388</v>
       </c>
       <c r="AQ2">
-        <v>-0.8420316491544428</v>
+        <v>-0.4986695050558808</v>
       </c>
     </row>
     <row r="3">
@@ -704,25 +710,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.107</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1291201593040927</v>
+        <v>0.2033078043508904</v>
       </c>
       <c r="H3">
-        <v>-0.02269035266991563</v>
+        <v>0.01155852088521355</v>
       </c>
       <c r="I3">
-        <v>-0.07430697479431955</v>
+        <v>-0.04402574824977681</v>
       </c>
       <c r="J3">
-        <v>-0.07430697479431955</v>
+        <v>-0.04402574824977681</v>
       </c>
       <c r="K3">
-        <v>-330.2</v>
+        <v>-251.7</v>
       </c>
       <c r="L3">
-        <v>-0.1730335901063774</v>
+        <v>-0.1182634027157825</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,183 +752,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>663.6</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.2803667244074528</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.3775008574368355</v>
+        <v>-0.2431414219474498</v>
       </c>
       <c r="X3">
-        <v>0.1217896710187427</v>
+        <v>0.1553075502293048</v>
       </c>
       <c r="Y3">
-        <v>-0.4992905284555782</v>
+        <v>-0.3984489721767546</v>
       </c>
       <c r="Z3">
-        <v>1.056878599911387</v>
+        <v>1.105782719384839</v>
       </c>
       <c r="AA3">
-        <v>-0.07853345148427114</v>
+        <v>-0.04868291162259053</v>
       </c>
       <c r="AB3">
-        <v>0.1074361893338245</v>
+        <v>0.105729775026532</v>
       </c>
       <c r="AC3">
-        <v>-0.1859696408180956</v>
+        <v>-0.1544126866491225</v>
       </c>
       <c r="AD3">
-        <v>1553.1</v>
+        <v>1831.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1553.1</v>
+        <v>1831.5</v>
       </c>
       <c r="AG3">
-        <v>889.4999999999999</v>
+        <v>1831.5</v>
       </c>
       <c r="AH3">
-        <v>0.3961989795918367</v>
+        <v>0.5947780339687591</v>
       </c>
       <c r="AI3">
-        <v>0.6000463624773016</v>
+        <v>0.6422710057511573</v>
       </c>
       <c r="AJ3">
-        <v>0.2731544036359169</v>
+        <v>0.5947780339687591</v>
       </c>
       <c r="AK3">
-        <v>0.4621499454460435</v>
+        <v>0.6422710057511573</v>
       </c>
       <c r="AL3">
-        <v>176.7</v>
+        <v>206</v>
       </c>
       <c r="AM3">
-        <v>173.04</v>
-      </c>
-      <c r="AN3">
-        <v>50.09999999999999</v>
+        <v>187.9</v>
       </c>
       <c r="AO3">
-        <v>-0.8024900962082627</v>
-      </c>
-      <c r="AP3">
-        <v>28.69354838709677</v>
+        <v>-0.4548543689320388</v>
       </c>
       <c r="AQ3">
-        <v>-0.8194637078132225</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Aurrigo International plc (AIM:AURR)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Auto &amp; Truck</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-0.1744845360824742</v>
-      </c>
-      <c r="H4">
-        <v>-0.2216494845360825</v>
-      </c>
-      <c r="I4">
-        <v>-0.5012886597938144</v>
-      </c>
-      <c r="J4">
-        <v>-0.5012886597938144</v>
-      </c>
-      <c r="K4">
-        <v>-4.91</v>
-      </c>
-      <c r="L4">
-        <v>-0.6327319587628867</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>3.55</v>
-      </c>
-      <c r="V4">
-        <v>0.06723484848484848</v>
-      </c>
-      <c r="X4">
-        <v>0.09506051400599939</v>
-      </c>
-      <c r="AB4">
-        <v>0.09430200204666304</v>
-      </c>
-      <c r="AD4">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="AG4">
-        <v>-2.737</v>
-      </c>
-      <c r="AH4">
-        <v>0.0151642325555369</v>
-      </c>
-      <c r="AI4">
-        <v>0.08600444303395746</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.05467111439586122</v>
-      </c>
-      <c r="AK4">
-        <v>-0.4636625444689141</v>
-      </c>
-      <c r="AL4">
-        <v>0.047</v>
-      </c>
-      <c r="AM4">
-        <v>-0.018</v>
-      </c>
-      <c r="AN4">
-        <v>-0.2227397260273973</v>
-      </c>
-      <c r="AO4">
-        <v>-82.76595744680851</v>
-      </c>
-      <c r="AP4">
-        <v>0.7498630136986302</v>
-      </c>
-      <c r="AQ4">
-        <v>216.1111111111111</v>
+        <v>-0.4986695050558808</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_auto_truck.xlsx
@@ -639,10 +639,10 @@
         <v>-0.2431414219474498</v>
       </c>
       <c r="X2">
-        <v>0.1553075502293048</v>
+        <v>0.1552564091237189</v>
       </c>
       <c r="Y2">
-        <v>-0.3984489721767546</v>
+        <v>-0.3983978310711687</v>
       </c>
       <c r="Z2">
         <v>1.105782719384839</v>
@@ -651,10 +651,10 @@
         <v>-0.04868291162259053</v>
       </c>
       <c r="AB2">
-        <v>0.105729775026532</v>
+        <v>0.1057090515271815</v>
       </c>
       <c r="AC2">
-        <v>-0.1544126866491225</v>
+        <v>-0.154391963149772</v>
       </c>
       <c r="AD2">
         <v>1831.5</v>
@@ -761,10 +761,10 @@
         <v>-0.2431414219474498</v>
       </c>
       <c r="X3">
-        <v>0.1553075502293048</v>
+        <v>0.1552564091237189</v>
       </c>
       <c r="Y3">
-        <v>-0.3984489721767546</v>
+        <v>-0.3983978310711687</v>
       </c>
       <c r="Z3">
         <v>1.105782719384839</v>
@@ -773,10 +773,10 @@
         <v>-0.04868291162259053</v>
       </c>
       <c r="AB3">
-        <v>0.105729775026532</v>
+        <v>0.1057090515271815</v>
       </c>
       <c r="AC3">
-        <v>-0.1544126866491225</v>
+        <v>-0.154391963149772</v>
       </c>
       <c r="AD3">
         <v>1831.5</v>
